--- a/data/print_templates/B__packing_list_shipment__shipment.xlsx
+++ b/data/print_templates/B__packing_list_shipment__shipment.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/EdouardGonnu/asf-wms/data/print_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB37CC2F-B8AB-9C47-829F-A58AB59983B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F75DF9-C0EF-CB4E-855F-C23342083E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16940" xr2:uid="{D41FDF60-E254-7C4C-BFC3-DDF9FE3B5742}"/>
+    <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16940" xr2:uid="{D41FDF60-E254-7C4C-BFC3-DDF9FE3B5742}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Feuil1!$A$1:$F$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Feuil1!$A$1:$E$23</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>QUANTITE</t>
   </si>
@@ -47,16 +47,10 @@
     <t>COLIS N°</t>
   </si>
   <si>
-    <t>ORIGINE DES PRODUITS</t>
-  </si>
-  <si>
     <t>NOMBRE DE COLIS</t>
   </si>
   <si>
     <t>Dons humanitaires non destinés à être revendus - Produits non dangereux</t>
-  </si>
-  <si>
-    <t>FORME</t>
   </si>
   <si>
     <t>PRODUIT</t>
@@ -68,13 +62,16 @@
     <t>N° DE LOT</t>
   </si>
   <si>
-    <t>ESCALE</t>
-  </si>
-  <si>
     <t>DESTINATAIRE</t>
   </si>
   <si>
-    <t>DONS fait en FRANCE</t>
+    <t>LISTE DE COLISAGE</t>
+  </si>
+  <si>
+    <t>Origine des dons : France</t>
+  </si>
+  <si>
+    <t>DESTINATION</t>
   </si>
 </sst>
 </file>
@@ -107,20 +104,22 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Cambria"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="28"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="14"/>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
-      <name val="Aptos"/>
+      <name val="Cambria"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -137,18 +136,9 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top/>
       <bottom/>
@@ -173,75 +163,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Aptos"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <font>
         <b val="0"/>
@@ -424,23 +376,6 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -525,25 +460,20 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>952500</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>192534</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="968000" cy="589817"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Image 2">
+        <xdr:cNvPr id="2" name="Image 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9F5A5F4-990E-0D00-E8CE-0986E50814ED}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{652A2DB2-4885-494E-A727-A3BE02D8B32D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -551,22 +481,15 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect t="18570" b="15109"/>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2717800" y="215900"/>
-          <a:ext cx="3225800" cy="992634"/>
+          <a:off x="279400" y="215900"/>
+          <a:ext cx="968000" cy="589817"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -574,33 +497,31 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{86EF37FB-E506-1E4C-98B6-94A9E27D3858}" name="Tableau2" displayName="Tableau2" ref="A12:E22" totalsRowShown="0" headerRowDxfId="12">
-  <autoFilter ref="A12:E22" xr:uid="{86EF37FB-E506-1E4C-98B6-94A9E27D3858}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{54CAC0AE-8B46-D448-A075-A10313DB52BC}" name="COLIS N°" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{BBFB573B-AD59-804B-B19E-5E817460BD0B}" name="FORME" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{FBFF4320-0029-1F4A-80B8-9873748E956F}" name="PRODUIT" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{6694315A-10C9-2A4F-9F6E-2A7012ED73F4}" name="QUANTITE" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{3957F165-746F-D343-A9EF-25CE93FC4BC3}" name="DATE LIMITE" dataDxfId="7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{86EF37FB-E506-1E4C-98B6-94A9E27D3858}" name="Tableau2" displayName="Tableau2" ref="A12:D22" totalsRowShown="0" headerRowDxfId="10">
+  <autoFilter ref="A12:D22" xr:uid="{86EF37FB-E506-1E4C-98B6-94A9E27D3858}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{54CAC0AE-8B46-D448-A075-A10313DB52BC}" name="COLIS N°" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{BBFB573B-AD59-804B-B19E-5E817460BD0B}" name="PRODUIT" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{FBFF4320-0029-1F4A-80B8-9873748E956F}" name="QUANTITE" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{6694315A-10C9-2A4F-9F6E-2A7012ED73F4}" name="DATE LIMITE" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A2FC5B0B-81A3-7340-86EB-1B51672D75B6}" name="Tableau3" displayName="Tableau3" ref="A8:E9" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A8:E9" xr:uid="{A2FC5B0B-81A3-7340-86EB-1B51672D75B6}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E35141A4-9B40-BB49-A0ED-D3E8753F2B81}" name="N° DE LOT" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{B7C97902-2DD4-774D-A014-E20027884A92}" name="NOMBRE DE COLIS" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{E8CB8828-A0E5-8D4A-9866-36313FB5EFA1}" name="ESCALE" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{F557127E-D325-654A-BE09-328E1D31C14A}" name="DESTINATAIRE" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{10461B48-46E8-9146-88F8-32E8CA3832C0}" name="ORIGINE DES PRODUITS" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A2FC5B0B-81A3-7340-86EB-1B51672D75B6}" name="Tableau3" displayName="Tableau3" ref="A9:D10" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="A9:D10" xr:uid="{A2FC5B0B-81A3-7340-86EB-1B51672D75B6}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{E35141A4-9B40-BB49-A0ED-D3E8753F2B81}" name="N° DE LOT" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{B7C97902-2DD4-774D-A014-E20027884A92}" name="NOMBRE DE COLIS" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{E8CB8828-A0E5-8D4A-9866-36313FB5EFA1}" name="DESTINATION" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{F557127E-D325-654A-BE09-328E1D31C14A}" name="DESTINATAIRE" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -926,174 +847,154 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:E22"/>
+  <dimension ref="A2:D22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="5" width="23.1640625" customWidth="1"/>
-    <col min="6" max="6" width="2.83203125" customWidth="1"/>
+    <col min="1" max="4" width="23.1640625" customWidth="1"/>
+    <col min="5" max="5" width="2.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-    </row>
-    <row r="8" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+    <row r="2" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+    </row>
+    <row r="3" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+    </row>
+    <row r="4" spans="1:4" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+    </row>
+    <row r="5" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+    </row>
+    <row r="7" spans="1:4" ht="21" x14ac:dyDescent="0.2">
+      <c r="A7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+    </row>
+    <row r="9" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>2</v>
+      <c r="D9" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="40" x14ac:dyDescent="0.2">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-    </row>
-    <row r="12" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="22" x14ac:dyDescent="0.2">
+      <c r="A10" s="3"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="12" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="5"/>
       <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="5"/>
       <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="5"/>
       <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="5"/>
       <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" s="6"/>
       <c r="C17" s="5"/>
       <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="B18" s="6"/>
       <c r="C18" s="5"/>
       <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" s="6"/>
       <c r="C19" s="5"/>
       <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" s="6"/>
       <c r="C20" s="5"/>
       <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
       <c r="B21" s="6"/>
       <c r="C21" s="5"/>
       <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="5"/>
       <c r="B22" s="6"/>
       <c r="C22" s="5"/>
       <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A2:E6"/>
+  <mergeCells count="3">
+    <mergeCell ref="A2:D4"/>
+    <mergeCell ref="A5:D6"/>
+    <mergeCell ref="A7:D7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="11" scale="69" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
